--- a/tools/excel-config/enemy.xlsx
+++ b/tools/excel-config/enemy.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -487,27 +487,32 @@
           <t>colorHex</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>baseArt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hpPerCell</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>coin</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -529,27 +534,32 @@
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -568,30 +578,35 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>染色色值（零美术方案：同一贴图按品质染色）</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+          <t>染色色值（UI / 掉落物染色仍可用）</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>品质底图贴图名（一格一张，128×128）</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>单格血量（约 ×1.65 几何递增）</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>生成权重（越大越常见）</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>单格基础经验</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>单格基础金币</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -611,19 +626,24 @@
           <t>#FFFFFF</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>最弱的杂兵，教学期主力</t>
         </is>
@@ -643,19 +663,24 @@
           <t>#4CD964</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>25</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>基础档</t>
         </is>
@@ -675,19 +700,24 @@
           <t>#3B82F6</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>需要两三发</t>
         </is>
@@ -707,19 +737,24 @@
           <t>#A855F7</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>明显更硬，见到要优先处理</t>
         </is>
@@ -739,19 +774,24 @@
           <t>#F5C542</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>小高潮</t>
         </is>
@@ -771,19 +811,24 @@
           <t>#EF4444</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>稀有，见到即高价值目标</t>
         </is>
@@ -1084,7 +1129,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>贴图名（零美术方案：按品质染色）</t>
+          <t>怪物贴图名（monster_0001-0010 普通/精英；Boss_001-003 四/六/八格）</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1190,7 +1235,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>enemy_white</t>
+          <t>monster_0001</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
@@ -1266,7 +1311,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>enemy_green</t>
+          <t>monster_0002</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
@@ -1342,7 +1387,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>enemy_green</t>
+          <t>monster_0003</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
@@ -1418,7 +1463,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>enemy_blue</t>
+          <t>monster_0004</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
@@ -1494,7 +1539,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>enemy_purple</t>
+          <t>monster_0005</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -1570,7 +1615,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>enemy_gold</t>
+          <t>monster_0006</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
@@ -1646,7 +1691,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>enemy_blue</t>
+          <t>Boss_001</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
@@ -1722,7 +1767,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>enemy_red</t>
+          <t>Boss_002</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
@@ -1798,7 +1843,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>enemy_red</t>
+          <t>Boss_003</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
